--- a/LLM-Showdown.xlsx
+++ b/LLM-Showdown.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebas\Documents\FederalAI\Zusatzzeuch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LAB\SuperCalc Sicherheitsbenchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E5D636-C32B-454D-A88F-8EFB0D7E8B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3928A3-F06E-4F10-907A-561CB5B47183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10065" yWindow="3045" windowWidth="35010" windowHeight="15885" xr2:uid="{52DCE92F-6A73-4A95-9A5F-EEA0CB0D44BF}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>Qwen3.5-9B-Q8_0</t>
   </si>
   <si>
-    <t>SuperCalc Sicherheitsbenchmark</t>
-  </si>
-  <si>
     <t>Validierung gegen MD</t>
   </si>
   <si>
@@ -267,6 +264,9 @@
   </si>
   <si>
     <t>14/15</t>
+  </si>
+  <si>
+    <t>SuperCalc Sicherheitsbenchmark v0.1</t>
   </si>
 </sst>
 </file>
@@ -997,46 +997,46 @@
   <sheetData>
     <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>20</v>
-      </c>
       <c r="D1" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>20</v>
-      </c>
       <c r="G1" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L1" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1054,19 +1054,19 @@
         <v>5</v>
       </c>
       <c r="F2" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>0</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K2" s="19" t="s">
         <v>1</v>
@@ -1075,15 +1075,15 @@
         <v>6</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N2" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1101,95 +1101,95 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>28</v>
-      </c>
       <c r="N4" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="17" t="s">
+      <c r="H5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>73</v>
-      </c>
       <c r="M5" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1207,95 +1207,95 @@
     </row>
     <row r="7" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="F7" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="G7" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>46</v>
-      </c>
       <c r="H7" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" s="29" t="s">
-        <v>52</v>
-      </c>
       <c r="L7" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="29" t="s">
-        <v>56</v>
-      </c>
       <c r="N7" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>10</v>
-      </c>
       <c r="E8" s="35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="35" t="s">
-        <v>35</v>
-      </c>
       <c r="H8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="35" t="s">
-        <v>18</v>
-      </c>
       <c r="L8" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N8" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="13">
         <f>B8/B7</f>
@@ -1352,51 +1352,51 @@
     </row>
     <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>42</v>
-      </c>
       <c r="E10" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="G10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="H10" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>50</v>
-      </c>
       <c r="I10" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K10" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="31" t="s">
         <v>53</v>
-      </c>
-      <c r="L10" s="31" t="s">
-        <v>54</v>
       </c>
       <c r="M10" s="31">
         <v>36</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="36">
         <v>3712</v>
@@ -1432,15 +1432,15 @@
         <v>2391</v>
       </c>
       <c r="M11" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="13">
         <f>B11/B10</f>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="14" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="33">
         <v>130</v>
@@ -1536,13 +1536,13 @@
         <v>2</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K14" s="33">
         <v>37</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="37">
         <v>8863</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="16" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="13">
         <f>B15/B14</f>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="17" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="34">
         <v>115</v>
@@ -1699,12 +1699,12 @@
         <v>2</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="37">
         <v>7368</v>
@@ -1743,12 +1743,12 @@
         <v>7346</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="25">
         <f>B18/B17</f>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="27">
         <f>B18+B15+B11+B8</f>

--- a/LLM-Showdown.xlsx
+++ b/LLM-Showdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LAB\SuperCalc Sicherheitsbenchmark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitHub\SuperCalc Sicherheitsbenchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3928A3-F06E-4F10-907A-561CB5B47183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CA456C-F2A4-4EF2-B822-34347D4D8FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10065" yWindow="3045" windowWidth="35010" windowHeight="15885" xr2:uid="{52DCE92F-6A73-4A95-9A5F-EEA0CB0D44BF}"/>
+    <workbookView xWindow="7410" yWindow="675" windowWidth="38700" windowHeight="14985" xr2:uid="{52DCE92F-6A73-4A95-9A5F-EEA0CB0D44BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
   <si>
     <t>Devstral-Small-2-24B-Instruct-2512-IQ4_XS-4.04bpw</t>
   </si>
@@ -267,13 +267,34 @@
   </si>
   <si>
     <t>SuperCalc Sicherheitsbenchmark v0.1</t>
+  </si>
+  <si>
+    <t>Dense-Hybrid</t>
+  </si>
+  <si>
+    <t>gemma-4-12b-it-bf16</t>
+  </si>
+  <si>
+    <t>9,8</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>2717</t>
+  </si>
+  <si>
+    <t>4/20</t>
+  </si>
+  <si>
+    <t>138</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,6 +382,12 @@
       <color theme="1"/>
       <name val="Microsoft New Tai Lue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -977,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04619A31-C7C3-495B-9122-319EFBF9560B}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -985,17 +1012,18 @@
     <col min="3" max="3" width="32.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="59" style="2" customWidth="1"/>
-    <col min="11" max="11" width="43.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="2"/>
+    <col min="6" max="6" width="28" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="59" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="59" style="2" customWidth="1"/>
+    <col min="12" max="12" width="43.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>35</v>
       </c>
@@ -1012,13 +1040,13 @@
         <v>18</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>18</v>
+      <c r="H1" s="20" t="s">
+        <v>19</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>18</v>
@@ -1029,7 +1057,7 @@
       <c r="K1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="18" t="s">
         <v>18</v>
       </c>
       <c r="M1" s="22" t="s">
@@ -1038,8 +1066,11 @@
       <c r="N1" s="22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="39"/>
       <c r="B2" s="23" t="s">
         <v>2</v>
@@ -1054,34 +1085,37 @@
         <v>5</v>
       </c>
       <c r="F2" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="N2" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="O2" s="23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>75</v>
       </c>
@@ -1098,8 +1132,9 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>15</v>
       </c>
@@ -1115,35 +1150,36 @@
       <c r="E4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="H4" s="15" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>24</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="L4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="N4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="O4" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
@@ -1159,14 +1195,12 @@
       <c r="E5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>74</v>
@@ -1178,16 +1212,19 @@
         <v>74</v>
       </c>
       <c r="L5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="N5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="O5" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -1204,8 +1241,9 @@
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="9"/>
+    </row>
+    <row r="7" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>56</v>
       </c>
@@ -1221,35 +1259,36 @@
       <c r="E7" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="29"/>
+      <c r="G7" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="I7" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="J7" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="K7" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="L7" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="M7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="N7" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="O7" s="29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1265,35 +1304,36 @@
       <c r="E8" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="35"/>
+      <c r="G8" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="H8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="I8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="J8" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="K8" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="L8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="M8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="N8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="35" t="s">
+      <c r="O8" s="35" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>36</v>
       </c>
@@ -1302,7 +1342,7 @@
         <v>6.8508771929824563</v>
       </c>
       <c r="C9" s="13">
-        <f t="shared" ref="C9:N9" si="0">C8/C7</f>
+        <f t="shared" ref="C9:O9" si="0">C8/C7</f>
         <v>43.516339869281047</v>
       </c>
       <c r="D9" s="13">
@@ -1313,44 +1353,48 @@
         <f t="shared" si="0"/>
         <v>33.217948717948715</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="13" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="13">
         <f t="shared" si="0"/>
         <v>75.293103448275858</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="13">
         <f t="shared" si="0"/>
         <v>87.564516129032256</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="13">
         <f t="shared" si="0"/>
         <v>15.295454545454545</v>
       </c>
-      <c r="I9" s="13">
+      <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>5.5365853658536581</v>
       </c>
-      <c r="J9" s="13">
+      <c r="K9" s="13">
         <f t="shared" si="0"/>
         <v>11.669354838709678</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <f t="shared" si="0"/>
         <v>22.818652849740932</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <f t="shared" si="0"/>
         <v>57.797687861271676</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <f t="shared" si="0"/>
         <v>92.838095238095235</v>
       </c>
-      <c r="N9" s="13" t="e">
+      <c r="O9" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>57</v>
       </c>
@@ -1366,35 +1410,36 @@
       <c r="E10" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="31"/>
+      <c r="G10" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="H10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="I10" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="J10" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="K10" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="K10" s="31" t="s">
+      <c r="L10" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="31" t="s">
+      <c r="M10" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="31">
+      <c r="N10" s="31">
         <v>36</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="O10" s="31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
@@ -1410,35 +1455,36 @@
       <c r="E11" s="36">
         <v>2152</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="36"/>
+      <c r="G11" s="36">
         <v>2120</v>
       </c>
-      <c r="G11" s="36">
+      <c r="H11" s="36">
         <v>1948</v>
       </c>
-      <c r="H11" s="36">
+      <c r="I11" s="36">
         <v>1352</v>
       </c>
-      <c r="I11" s="36">
+      <c r="J11" s="36">
         <v>1709</v>
       </c>
-      <c r="J11" s="36">
+      <c r="K11" s="36">
         <v>1574</v>
       </c>
-      <c r="K11" s="36">
+      <c r="L11" s="36">
         <v>1406</v>
       </c>
-      <c r="L11" s="36">
+      <c r="M11" s="36">
         <v>2391</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="N11" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="N11" s="36" t="s">
+      <c r="O11" s="36" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>36</v>
       </c>
@@ -1447,7 +1493,7 @@
         <v>6.5122807017543858</v>
       </c>
       <c r="C12" s="13">
-        <f t="shared" ref="C12:N12" si="1">C11/C10</f>
+        <f t="shared" ref="C12:O12" si="1">C11/C10</f>
         <v>43.47</v>
       </c>
       <c r="D12" s="13">
@@ -1458,44 +1504,48 @@
         <f t="shared" si="1"/>
         <v>50.046511627906973</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="13">
         <f t="shared" si="1"/>
         <v>73.103448275862064</v>
       </c>
-      <c r="G12" s="13">
+      <c r="H12" s="13">
         <f t="shared" si="1"/>
         <v>88.545454545454547</v>
       </c>
-      <c r="H12" s="13">
+      <c r="I12" s="13">
         <f t="shared" si="1"/>
         <v>12.18018018018018</v>
       </c>
-      <c r="I12" s="13">
+      <c r="J12" s="13">
         <f t="shared" si="1"/>
         <v>5.0412979351032448</v>
       </c>
-      <c r="J12" s="13">
+      <c r="K12" s="13">
         <f t="shared" si="1"/>
         <v>9.5975609756097562</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <f t="shared" si="1"/>
         <v>16.738095238095237</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>56.928571428571431</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <f t="shared" si="1"/>
         <v>93.027777777777771</v>
       </c>
-      <c r="N12" s="13" t="e">
+      <c r="O12" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
@@ -1512,8 +1562,9 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>56</v>
       </c>
@@ -1529,35 +1580,36 @@
       <c r="E14" s="33">
         <v>20</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="33"/>
+      <c r="G14" s="33">
         <v>2.5</v>
       </c>
-      <c r="G14" s="33">
+      <c r="H14" s="33">
         <v>2</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="I14" s="33" t="s">
         <v>69</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>60</v>
       </c>
       <c r="J14" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="33">
         <v>37</v>
       </c>
-      <c r="L14" s="33">
+      <c r="M14" s="33">
         <v>3.3</v>
       </c>
-      <c r="M14" s="33">
+      <c r="N14" s="33">
         <v>1.9</v>
       </c>
-      <c r="N14" s="33">
+      <c r="O14" s="33">
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>8</v>
       </c>
@@ -1573,26 +1625,24 @@
       <c r="E15" s="37">
         <v>9943</v>
       </c>
-      <c r="F15" s="37">
-        <v>9943</v>
-      </c>
+      <c r="F15" s="37"/>
       <c r="G15" s="37">
         <v>9943</v>
       </c>
       <c r="H15" s="37">
+        <v>9943</v>
+      </c>
+      <c r="I15" s="37">
         <v>8611</v>
       </c>
-      <c r="I15" s="37">
+      <c r="J15" s="37">
         <v>9163</v>
       </c>
-      <c r="J15" s="37">
+      <c r="K15" s="37">
         <v>8611</v>
       </c>
-      <c r="K15" s="37">
+      <c r="L15" s="37">
         <v>8734</v>
-      </c>
-      <c r="L15" s="37">
-        <v>8863</v>
       </c>
       <c r="M15" s="37">
         <v>8863</v>
@@ -1600,8 +1650,11 @@
       <c r="N15" s="37">
         <v>8863</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O15" s="37">
+        <v>8863</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>36</v>
       </c>
@@ -1610,7 +1663,7 @@
         <v>68.176923076923075</v>
       </c>
       <c r="C16" s="13">
-        <f t="shared" ref="C16:N16" si="2">C15/C14</f>
+        <f t="shared" ref="C16:O16" si="2">C15/C14</f>
         <v>422.04761904761904</v>
       </c>
       <c r="D16" s="13">
@@ -1621,44 +1674,48 @@
         <f t="shared" si="2"/>
         <v>497.15</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="13">
         <f t="shared" si="2"/>
         <v>3977.2</v>
       </c>
-      <c r="G16" s="13">
+      <c r="H16" s="13">
         <f t="shared" si="2"/>
         <v>4971.5</v>
       </c>
-      <c r="H16" s="13">
+      <c r="I16" s="13">
         <f t="shared" si="2"/>
         <v>574.06666666666672</v>
       </c>
-      <c r="I16" s="13">
+      <c r="J16" s="13">
         <f t="shared" si="2"/>
         <v>78.316239316239319</v>
       </c>
-      <c r="J16" s="13">
+      <c r="K16" s="13">
         <f t="shared" si="2"/>
         <v>73.598290598290603</v>
       </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <f t="shared" si="2"/>
         <v>236.05405405405406</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <f t="shared" si="2"/>
         <v>2685.757575757576</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <f t="shared" si="2"/>
         <v>4664.7368421052633</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <f t="shared" si="2"/>
         <v>11078.75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>57</v>
       </c>
@@ -1674,35 +1731,36 @@
       <c r="E17" s="34">
         <v>16</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="34"/>
+      <c r="G17" s="34">
         <v>3.5</v>
       </c>
-      <c r="G17" s="34">
+      <c r="H17" s="34">
         <v>2.7</v>
       </c>
-      <c r="H17" s="34">
+      <c r="I17" s="34">
         <v>14</v>
       </c>
-      <c r="I17" s="34">
+      <c r="J17" s="34">
         <v>65</v>
       </c>
-      <c r="J17" s="34">
+      <c r="K17" s="34">
         <v>93</v>
       </c>
-      <c r="K17" s="34">
+      <c r="L17" s="34">
         <v>24</v>
       </c>
-      <c r="L17" s="34">
+      <c r="M17" s="34">
         <v>3.4</v>
       </c>
-      <c r="M17" s="34">
+      <c r="N17" s="34">
         <v>2</v>
       </c>
-      <c r="N17" s="34" t="s">
+      <c r="O17" s="34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>8</v>
       </c>
@@ -1718,35 +1776,36 @@
       <c r="E18" s="37">
         <v>6894</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="37"/>
+      <c r="G18" s="37">
         <v>9205</v>
       </c>
-      <c r="G18" s="37">
+      <c r="H18" s="37">
         <v>8269</v>
       </c>
-      <c r="H18" s="37">
+      <c r="I18" s="37">
         <v>5914</v>
       </c>
-      <c r="I18" s="37">
+      <c r="J18" s="37">
         <v>4864</v>
       </c>
-      <c r="J18" s="37">
+      <c r="K18" s="37">
         <v>6354</v>
       </c>
-      <c r="K18" s="37">
+      <c r="L18" s="37">
         <v>4864</v>
       </c>
-      <c r="L18" s="37">
+      <c r="M18" s="37">
         <v>8119</v>
       </c>
-      <c r="M18" s="37">
+      <c r="N18" s="37">
         <v>7346</v>
       </c>
-      <c r="N18" s="37" t="s">
+      <c r="O18" s="37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>36</v>
       </c>
@@ -1755,7 +1814,7 @@
         <v>64.0695652173913</v>
       </c>
       <c r="C19" s="25">
-        <f t="shared" ref="C19:N19" si="3">C18/C17</f>
+        <f t="shared" ref="C19:O19" si="3">C18/C17</f>
         <v>397.31578947368422</v>
       </c>
       <c r="D19" s="25">
@@ -1766,44 +1825,48 @@
         <f t="shared" si="3"/>
         <v>430.875</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="25" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="25">
         <f t="shared" si="3"/>
         <v>2630</v>
       </c>
-      <c r="G19" s="25">
+      <c r="H19" s="25">
         <f t="shared" si="3"/>
         <v>3062.5925925925926</v>
       </c>
-      <c r="H19" s="25">
+      <c r="I19" s="25">
         <f t="shared" si="3"/>
         <v>422.42857142857144</v>
       </c>
-      <c r="I19" s="25">
+      <c r="J19" s="25">
         <f t="shared" si="3"/>
         <v>74.830769230769235</v>
       </c>
-      <c r="J19" s="25">
-        <f t="shared" ref="J19" si="4">J18/J17</f>
+      <c r="K19" s="25">
+        <f t="shared" ref="K19" si="4">K18/K17</f>
         <v>68.322580645161295</v>
       </c>
-      <c r="K19" s="25">
+      <c r="L19" s="25">
         <f t="shared" si="3"/>
         <v>202.66666666666666</v>
       </c>
-      <c r="L19" s="25">
+      <c r="M19" s="25">
         <f t="shared" si="3"/>
         <v>2387.9411764705883</v>
       </c>
-      <c r="M19" s="25">
+      <c r="N19" s="25">
         <f t="shared" si="3"/>
         <v>3673</v>
       </c>
-      <c r="N19" s="25" t="e">
+      <c r="O19" s="25" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>58</v>
       </c>
@@ -1812,7 +1875,7 @@
         <v>26972</v>
       </c>
       <c r="C20" s="27">
-        <f t="shared" ref="C20:N20" si="5">C18+C15+C11+C8</f>
+        <f t="shared" ref="C20:O20" si="5">C18+C15+C11+C8</f>
         <v>27417</v>
       </c>
       <c r="D20" s="27">
@@ -1825,45 +1888,622 @@
       </c>
       <c r="F20" s="27">
         <f t="shared" si="5"/>
-        <v>25635</v>
+        <v>0</v>
       </c>
       <c r="G20" s="27">
         <f t="shared" si="5"/>
-        <v>25589</v>
+        <v>25635</v>
       </c>
       <c r="H20" s="27">
         <f t="shared" si="5"/>
-        <v>17896</v>
+        <v>25589</v>
       </c>
       <c r="I20" s="27">
         <f t="shared" si="5"/>
+        <v>17896</v>
+      </c>
+      <c r="J20" s="27">
+        <f t="shared" si="5"/>
         <v>17552</v>
       </c>
-      <c r="J20" s="27">
-        <f t="shared" ref="J20" si="6">J18+J15+J11+J8</f>
+      <c r="K20" s="27">
+        <f t="shared" ref="K20" si="6">K18+K15+K11+K8</f>
         <v>19433</v>
       </c>
-      <c r="K20" s="27">
+      <c r="L20" s="27">
         <f t="shared" si="5"/>
         <v>19408</v>
       </c>
-      <c r="L20" s="27">
+      <c r="M20" s="27">
         <f t="shared" si="5"/>
         <v>29372</v>
       </c>
-      <c r="M20" s="27">
+      <c r="N20" s="27">
         <f t="shared" si="5"/>
         <v>29306</v>
       </c>
-      <c r="N20" s="27" t="e">
+      <c r="O20" s="27" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+    </row>
+    <row r="28" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="13" t="e">
+        <f>B27/B26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C28" s="13" t="e">
+        <f t="shared" ref="C28:O28" si="7">C27/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28" s="13">
+        <f t="shared" si="7"/>
+        <v>20.125925925925927</v>
+      </c>
+      <c r="G28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="13" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36">
+        <v>2775</v>
+      </c>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+    </row>
+    <row r="31" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="13" t="e">
+        <f>B30/B29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C31" s="13" t="e">
+        <f t="shared" ref="C31:O31" si="8">C30/C29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F31" s="13">
+        <f t="shared" si="8"/>
+        <v>20.108695652173914</v>
+      </c>
+      <c r="G31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O31" s="13" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+    </row>
+    <row r="33" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+    </row>
+    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37">
+        <v>8374</v>
+      </c>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+    </row>
+    <row r="35" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="13" t="e">
+        <f>B34/B33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C35" s="13" t="e">
+        <f t="shared" ref="C35:O35" si="9">C34/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F35" s="13">
+        <f t="shared" si="9"/>
+        <v>854.48979591836724</v>
+      </c>
+      <c r="G35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O35" s="13" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34">
+        <v>11</v>
+      </c>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+    </row>
+    <row r="37" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37">
+        <v>7539</v>
+      </c>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="37"/>
+    </row>
+    <row r="38" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="25" t="e">
+        <f>B37/B36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C38" s="25" t="e">
+        <f t="shared" ref="C38:O38" si="10">C37/C36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F38" s="25">
+        <f t="shared" si="10"/>
+        <v>685.36363636363637</v>
+      </c>
+      <c r="G38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O38" s="25" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="27">
+        <f>B37+B34+B30+B27</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="27">
+        <f t="shared" ref="C39:O39" si="11">C37+C34+C30+C27</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="27">
+        <f t="shared" si="11"/>
+        <v>21405</v>
+      </c>
+      <c r="G39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="27">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/LLM-Showdown.xlsx
+++ b/LLM-Showdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitHub\SuperCalc Sicherheitsbenchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CA456C-F2A4-4EF2-B822-34347D4D8FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E3FCB-EE80-4D12-97A4-EBBD9F82C0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7410" yWindow="675" windowWidth="38700" windowHeight="14985" xr2:uid="{52DCE92F-6A73-4A95-9A5F-EEA0CB0D44BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{52DCE92F-6A73-4A95-9A5F-EEA0CB0D44BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="81">
   <si>
     <t>Devstral-Small-2-24B-Instruct-2512-IQ4_XS-4.04bpw</t>
   </si>
@@ -126,12 +126,6 @@
   </si>
   <si>
     <t>3349</t>
-  </si>
-  <si>
-    <t>Qwen3.5-2B-Q8_0.gguf</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>gemma-4-E4B-it-Q8_0</t>
@@ -1004,28 +998,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04619A31-C7C3-495B-9122-319EFBF9560B}">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="59" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="59" style="2" customWidth="1"/>
-    <col min="12" max="12" width="43.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.42578125" style="2"/>
+    <col min="4" max="4" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="59" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="59" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>18</v>
@@ -1033,26 +1027,26 @@
       <c r="C1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>18</v>
       </c>
       <c r="K1" s="18" t="s">
         <v>18</v>
@@ -1060,17 +1054,14 @@
       <c r="L1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="39"/>
       <c r="B2" s="23" t="s">
         <v>2</v>
@@ -1078,46 +1069,43 @@
       <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="G2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>31</v>
-      </c>
       <c r="H2" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>64</v>
-      </c>
       <c r="L2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1132,9 +1120,8 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>15</v>
       </c>
@@ -1145,86 +1132,80 @@
         <v>23</v>
       </c>
       <c r="D4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="15"/>
       <c r="G4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="K4" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="L4" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="15" t="s">
+      <c r="M4" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="E5" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="K5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="L5" s="17" t="s">
         <v>72</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>72</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -1241,54 +1222,50 @@
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>39</v>
-      </c>
       <c r="D7" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="J7" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>62</v>
-      </c>
       <c r="K7" s="29" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1299,147 +1276,137 @@
         <v>10</v>
       </c>
       <c r="D8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="G8" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="35"/>
+      <c r="I8" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>34</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>36</v>
       </c>
       <c r="B9" s="13">
         <f>B8/B7</f>
         <v>6.8508771929824563</v>
       </c>
       <c r="C9" s="13">
-        <f t="shared" ref="C9:O9" si="0">C8/C7</f>
+        <f t="shared" ref="C9:N9" si="0">C8/C7</f>
         <v>43.516339869281047</v>
       </c>
       <c r="D9" s="13">
+        <f>D8/D7</f>
+        <v>57.797687861271676</v>
+      </c>
+      <c r="E9" s="13">
+        <f>E8/E7</f>
+        <v>92.838095238095235</v>
+      </c>
+      <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>9.1226611226611229</v>
       </c>
-      <c r="E9" s="13">
+      <c r="G9" s="13">
         <f t="shared" si="0"/>
         <v>33.217948717948715</v>
       </c>
-      <c r="F9" s="13" t="e">
+      <c r="H9" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G9" s="13">
+      <c r="I9" s="13">
         <f t="shared" si="0"/>
         <v>75.293103448275858</v>
       </c>
-      <c r="H9" s="13">
+      <c r="J9" s="13">
         <f t="shared" si="0"/>
         <v>87.564516129032256</v>
       </c>
-      <c r="I9" s="13">
+      <c r="K9" s="13">
         <f t="shared" si="0"/>
         <v>15.295454545454545</v>
       </c>
-      <c r="J9" s="13">
+      <c r="L9" s="13">
         <f t="shared" si="0"/>
         <v>5.5365853658536581</v>
       </c>
-      <c r="K9" s="13">
+      <c r="M9" s="13">
         <f t="shared" si="0"/>
         <v>11.669354838709678</v>
       </c>
-      <c r="L9" s="13">
+      <c r="N9" s="13">
         <f t="shared" si="0"/>
         <v>22.818652849740932</v>
       </c>
-      <c r="M9" s="13">
-        <f t="shared" si="0"/>
-        <v>57.797687861271676</v>
-      </c>
-      <c r="N9" s="13">
-        <f t="shared" si="0"/>
-        <v>92.838095238095235</v>
-      </c>
-      <c r="O9" s="13" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B10" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>40</v>
-      </c>
       <c r="D10" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="31">
+        <v>36</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31" t="s">
+      <c r="K10" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>68</v>
-      </c>
       <c r="L10" s="31" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="31">
-        <v>36</v>
-      </c>
-      <c r="O10" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
@@ -1450,102 +1417,95 @@
         <v>4347</v>
       </c>
       <c r="D11" s="36">
+        <v>2391</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="36">
         <v>1739</v>
       </c>
-      <c r="E11" s="36">
+      <c r="G11" s="36">
         <v>2152</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36">
         <v>2120</v>
       </c>
-      <c r="H11" s="36">
+      <c r="J11" s="36">
         <v>1948</v>
       </c>
-      <c r="I11" s="36">
+      <c r="K11" s="36">
         <v>1352</v>
       </c>
-      <c r="J11" s="36">
+      <c r="L11" s="36">
         <v>1709</v>
       </c>
-      <c r="K11" s="36">
+      <c r="M11" s="36">
         <v>1574</v>
       </c>
-      <c r="L11" s="36">
+      <c r="N11" s="36">
         <v>1406</v>
       </c>
-      <c r="M11" s="36">
-        <v>2391</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" s="36" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="13">
         <f>B11/B10</f>
         <v>6.5122807017543858</v>
       </c>
       <c r="C12" s="13">
-        <f t="shared" ref="C12:O12" si="1">C11/C10</f>
+        <f t="shared" ref="C12:N12" si="1">C11/C10</f>
         <v>43.47</v>
       </c>
       <c r="D12" s="13">
+        <f>D11/D10</f>
+        <v>56.928571428571431</v>
+      </c>
+      <c r="E12" s="13">
+        <f>E11/E10</f>
+        <v>93.027777777777771</v>
+      </c>
+      <c r="F12" s="13">
         <f t="shared" si="1"/>
         <v>8.4829268292682922</v>
       </c>
-      <c r="E12" s="13">
+      <c r="G12" s="13">
         <f t="shared" si="1"/>
         <v>50.046511627906973</v>
       </c>
-      <c r="F12" s="13" t="e">
+      <c r="H12" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G12" s="13">
+      <c r="I12" s="13">
         <f t="shared" si="1"/>
         <v>73.103448275862064</v>
       </c>
-      <c r="H12" s="13">
+      <c r="J12" s="13">
         <f t="shared" si="1"/>
         <v>88.545454545454547</v>
       </c>
-      <c r="I12" s="13">
+      <c r="K12" s="13">
         <f t="shared" si="1"/>
         <v>12.18018018018018</v>
       </c>
-      <c r="J12" s="13">
+      <c r="L12" s="13">
         <f t="shared" si="1"/>
         <v>5.0412979351032448</v>
       </c>
-      <c r="K12" s="13">
+      <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>9.5975609756097562</v>
       </c>
-      <c r="L12" s="13">
+      <c r="N12" s="13">
         <f t="shared" si="1"/>
         <v>16.738095238095237</v>
       </c>
-      <c r="M12" s="13">
-        <f t="shared" si="1"/>
-        <v>56.928571428571431</v>
-      </c>
-      <c r="N12" s="13">
-        <f t="shared" si="1"/>
-        <v>93.027777777777771</v>
-      </c>
-      <c r="O12" s="13" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
@@ -1562,11 +1522,10 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-    </row>
-    <row r="14" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14" s="33">
         <v>130</v>
@@ -1575,41 +1534,38 @@
         <v>21</v>
       </c>
       <c r="D14" s="33">
+        <v>3.3</v>
+      </c>
+      <c r="E14" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="F14" s="33">
         <v>165</v>
       </c>
-      <c r="E14" s="33">
+      <c r="G14" s="33">
         <v>20</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33">
+      <c r="H14" s="33"/>
+      <c r="I14" s="33">
         <v>2.5</v>
       </c>
-      <c r="H14" s="33">
+      <c r="J14" s="33">
         <v>2</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>60</v>
-      </c>
       <c r="K14" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="33">
+        <v>67</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="33">
         <v>37</v>
       </c>
-      <c r="M14" s="33">
-        <v>3.3</v>
-      </c>
-      <c r="N14" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="O14" s="33">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>8</v>
       </c>
@@ -1620,104 +1576,97 @@
         <v>8863</v>
       </c>
       <c r="D15" s="37">
+        <v>8863</v>
+      </c>
+      <c r="E15" s="37">
+        <v>8863</v>
+      </c>
+      <c r="F15" s="37">
         <v>9944</v>
       </c>
-      <c r="E15" s="37">
-        <v>9943</v>
-      </c>
-      <c r="F15" s="37"/>
       <c r="G15" s="37">
         <v>9943</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="37"/>
+      <c r="I15" s="37">
         <v>9943</v>
       </c>
-      <c r="I15" s="37">
-        <v>8611</v>
-      </c>
       <c r="J15" s="37">
-        <v>9163</v>
+        <v>9943</v>
       </c>
       <c r="K15" s="37">
         <v>8611</v>
       </c>
       <c r="L15" s="37">
+        <v>9163</v>
+      </c>
+      <c r="M15" s="37">
+        <v>8611</v>
+      </c>
+      <c r="N15" s="37">
         <v>8734</v>
       </c>
-      <c r="M15" s="37">
-        <v>8863</v>
-      </c>
-      <c r="N15" s="37">
-        <v>8863</v>
-      </c>
-      <c r="O15" s="37">
-        <v>8863</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="13">
         <f>B15/B14</f>
         <v>68.176923076923075</v>
       </c>
       <c r="C16" s="13">
-        <f t="shared" ref="C16:O16" si="2">C15/C14</f>
+        <f t="shared" ref="C16:N16" si="2">C15/C14</f>
         <v>422.04761904761904</v>
       </c>
       <c r="D16" s="13">
+        <f>D15/D14</f>
+        <v>2685.757575757576</v>
+      </c>
+      <c r="E16" s="13">
+        <f>E15/E14</f>
+        <v>4664.7368421052633</v>
+      </c>
+      <c r="F16" s="13">
         <f t="shared" si="2"/>
         <v>60.266666666666666</v>
       </c>
-      <c r="E16" s="13">
+      <c r="G16" s="13">
         <f t="shared" si="2"/>
         <v>497.15</v>
       </c>
-      <c r="F16" s="13" t="e">
+      <c r="H16" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="13">
+      <c r="I16" s="13">
         <f t="shared" si="2"/>
         <v>3977.2</v>
       </c>
-      <c r="H16" s="13">
+      <c r="J16" s="13">
         <f t="shared" si="2"/>
         <v>4971.5</v>
       </c>
-      <c r="I16" s="13">
+      <c r="K16" s="13">
         <f t="shared" si="2"/>
         <v>574.06666666666672</v>
       </c>
-      <c r="J16" s="13">
+      <c r="L16" s="13">
         <f t="shared" si="2"/>
         <v>78.316239316239319</v>
       </c>
-      <c r="K16" s="13">
+      <c r="M16" s="13">
         <f t="shared" si="2"/>
         <v>73.598290598290603</v>
       </c>
-      <c r="L16" s="13">
+      <c r="N16" s="13">
         <f t="shared" si="2"/>
         <v>236.05405405405406</v>
       </c>
-      <c r="M16" s="13">
-        <f t="shared" si="2"/>
-        <v>2685.757575757576</v>
-      </c>
-      <c r="N16" s="13">
-        <f t="shared" si="2"/>
-        <v>4664.7368421052633</v>
-      </c>
-      <c r="O16" s="13">
-        <f t="shared" si="2"/>
-        <v>11078.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B17" s="34">
         <v>115</v>
@@ -1726,41 +1675,38 @@
         <v>19</v>
       </c>
       <c r="D17" s="34">
+        <v>3.4</v>
+      </c>
+      <c r="E17" s="34">
+        <v>2</v>
+      </c>
+      <c r="F17" s="34">
         <v>132</v>
       </c>
-      <c r="E17" s="34">
+      <c r="G17" s="34">
         <v>16</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34">
+      <c r="H17" s="34"/>
+      <c r="I17" s="34">
         <v>3.5</v>
       </c>
-      <c r="H17" s="34">
+      <c r="J17" s="34">
         <v>2.7</v>
       </c>
-      <c r="I17" s="34">
+      <c r="K17" s="34">
         <v>14</v>
       </c>
-      <c r="J17" s="34">
+      <c r="L17" s="34">
         <v>65</v>
       </c>
-      <c r="K17" s="34">
+      <c r="M17" s="34">
         <v>93</v>
       </c>
-      <c r="L17" s="34">
+      <c r="N17" s="34">
         <v>24</v>
       </c>
-      <c r="M17" s="34">
-        <v>3.4</v>
-      </c>
-      <c r="N17" s="34">
-        <v>2</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>8</v>
       </c>
@@ -1771,165 +1717,154 @@
         <v>7549</v>
       </c>
       <c r="D18" s="37">
+        <v>8119</v>
+      </c>
+      <c r="E18" s="37">
+        <v>7346</v>
+      </c>
+      <c r="F18" s="37">
         <v>7335</v>
       </c>
-      <c r="E18" s="37">
+      <c r="G18" s="37">
         <v>6894</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37">
+      <c r="H18" s="37"/>
+      <c r="I18" s="37">
         <v>9205</v>
       </c>
-      <c r="H18" s="37">
+      <c r="J18" s="37">
         <v>8269</v>
       </c>
-      <c r="I18" s="37">
+      <c r="K18" s="37">
         <v>5914</v>
-      </c>
-      <c r="J18" s="37">
-        <v>4864</v>
-      </c>
-      <c r="K18" s="37">
-        <v>6354</v>
       </c>
       <c r="L18" s="37">
         <v>4864</v>
       </c>
       <c r="M18" s="37">
-        <v>8119</v>
+        <v>6354</v>
       </c>
       <c r="N18" s="37">
-        <v>7346</v>
-      </c>
-      <c r="O18" s="37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>4864</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" s="25">
         <f>B18/B17</f>
         <v>64.0695652173913</v>
       </c>
       <c r="C19" s="25">
-        <f t="shared" ref="C19:O19" si="3">C18/C17</f>
+        <f t="shared" ref="C19:N19" si="3">C18/C17</f>
         <v>397.31578947368422</v>
       </c>
       <c r="D19" s="25">
+        <f>D18/D17</f>
+        <v>2387.9411764705883</v>
+      </c>
+      <c r="E19" s="25">
+        <f>E18/E17</f>
+        <v>3673</v>
+      </c>
+      <c r="F19" s="25">
         <f t="shared" si="3"/>
         <v>55.56818181818182</v>
       </c>
-      <c r="E19" s="25">
+      <c r="G19" s="25">
         <f t="shared" si="3"/>
         <v>430.875</v>
       </c>
-      <c r="F19" s="25" t="e">
+      <c r="H19" s="25" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="25">
+      <c r="I19" s="25">
         <f t="shared" si="3"/>
         <v>2630</v>
       </c>
-      <c r="H19" s="25">
+      <c r="J19" s="25">
         <f t="shared" si="3"/>
         <v>3062.5925925925926</v>
       </c>
-      <c r="I19" s="25">
+      <c r="K19" s="25">
         <f t="shared" si="3"/>
         <v>422.42857142857144</v>
       </c>
-      <c r="J19" s="25">
+      <c r="L19" s="25">
         <f t="shared" si="3"/>
         <v>74.830769230769235</v>
       </c>
-      <c r="K19" s="25">
-        <f t="shared" ref="K19" si="4">K18/K17</f>
+      <c r="M19" s="25">
+        <f t="shared" ref="M19" si="4">M18/M17</f>
         <v>68.322580645161295</v>
       </c>
-      <c r="L19" s="25">
+      <c r="N19" s="25">
         <f t="shared" si="3"/>
         <v>202.66666666666666</v>
       </c>
-      <c r="M19" s="25">
-        <f t="shared" si="3"/>
-        <v>2387.9411764705883</v>
-      </c>
-      <c r="N19" s="25">
-        <f t="shared" si="3"/>
-        <v>3673</v>
-      </c>
-      <c r="O19" s="25" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="27">
         <f>B18+B15+B11+B8</f>
         <v>26972</v>
       </c>
       <c r="C20" s="27">
-        <f t="shared" ref="C20:O20" si="5">C18+C15+C11+C8</f>
+        <f t="shared" ref="C20:N20" si="5">C18+C15+C11+C8</f>
         <v>27417</v>
       </c>
       <c r="D20" s="27">
+        <f>D18+D15+D11+D8</f>
+        <v>29372</v>
+      </c>
+      <c r="E20" s="27">
+        <f>E18+E15+E11+E8</f>
+        <v>29306</v>
+      </c>
+      <c r="F20" s="27">
         <f t="shared" si="5"/>
         <v>23406</v>
       </c>
-      <c r="E20" s="27">
+      <c r="G20" s="27">
         <f t="shared" si="5"/>
         <v>24171</v>
       </c>
-      <c r="F20" s="27">
+      <c r="H20" s="27">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G20" s="27">
+      <c r="I20" s="27">
         <f t="shared" si="5"/>
         <v>25635</v>
       </c>
-      <c r="H20" s="27">
+      <c r="J20" s="27">
         <f t="shared" si="5"/>
         <v>25589</v>
       </c>
-      <c r="I20" s="27">
+      <c r="K20" s="27">
         <f t="shared" si="5"/>
         <v>17896</v>
       </c>
-      <c r="J20" s="27">
+      <c r="L20" s="27">
         <f t="shared" si="5"/>
         <v>17552</v>
       </c>
-      <c r="K20" s="27">
-        <f t="shared" ref="K20" si="6">K18+K15+K11+K8</f>
+      <c r="M20" s="27">
+        <f t="shared" ref="M20" si="6">M18+M15+M11+M8</f>
         <v>19433</v>
       </c>
-      <c r="L20" s="27">
+      <c r="N20" s="27">
         <f t="shared" si="5"/>
         <v>19408</v>
       </c>
-      <c r="M20" s="27">
-        <f t="shared" si="5"/>
-        <v>29372</v>
-      </c>
-      <c r="N20" s="27">
-        <f t="shared" si="5"/>
-        <v>29306</v>
-      </c>
-      <c r="O20" s="27" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1944,9 +1879,8 @@
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>15</v>
       </c>
@@ -1954,20 +1888,19 @@
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>7</v>
       </c>
@@ -1975,20 +1908,19 @@
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="17" t="s">
-        <v>81</v>
-      </c>
+      <c r="F24" s="17"/>
       <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="H24" s="17" t="s">
+        <v>79</v>
+      </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -2005,30 +1937,28 @@
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-    </row>
-    <row r="26" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
       <c r="E26" s="29"/>
-      <c r="F26" s="29" t="s">
-        <v>79</v>
-      </c>
+      <c r="F26" s="29"/>
       <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
+      <c r="H26" s="29" t="s">
+        <v>77</v>
+      </c>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
       <c r="K26" s="29"/>
       <c r="L26" s="29"/>
       <c r="M26" s="29"/>
       <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>8</v>
       </c>
@@ -2036,51 +1966,50 @@
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
       <c r="E27" s="35"/>
-      <c r="F27" s="35" t="s">
-        <v>80</v>
-      </c>
+      <c r="F27" s="35"/>
       <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
+      <c r="H27" s="35" t="s">
+        <v>78</v>
+      </c>
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
       <c r="M27" s="35"/>
       <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-    </row>
-    <row r="28" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="13" t="e">
         <f>B27/B26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C28" s="13" t="e">
-        <f t="shared" ref="C28:O28" si="7">C27/C26</f>
+        <f t="shared" ref="C28:N28" si="7">C27/C26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="13" t="e">
+        <f>D27/D26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E28" s="13" t="e">
+        <f>E27/E26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F28" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="13" t="e">
+      <c r="G28" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F28" s="13">
+      <c r="H28" s="13">
         <f t="shared" si="7"/>
         <v>20.125925925925927</v>
       </c>
-      <c r="G28" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H28" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="I28" s="13" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -2105,33 +2034,28 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="13" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
-      <c r="F29" s="31" t="s">
-        <v>82</v>
-      </c>
+      <c r="F29" s="31"/>
       <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
+      <c r="H29" s="31" t="s">
+        <v>80</v>
+      </c>
       <c r="I29" s="31"/>
       <c r="J29" s="31"/>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -2139,51 +2063,50 @@
       <c r="C30" s="36"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
-      <c r="F30" s="36">
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36">
         <v>2775</v>
       </c>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
       <c r="I30" s="36"/>
       <c r="J30" s="36"/>
       <c r="K30" s="36"/>
       <c r="L30" s="36"/>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-    </row>
-    <row r="31" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B31" s="13" t="e">
         <f>B30/B29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C31" s="13" t="e">
-        <f t="shared" ref="C31:O31" si="8">C30/C29</f>
+        <f t="shared" ref="C31:N31" si="8">C30/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="13" t="e">
+        <f>D30/D29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="13" t="e">
+        <f>E30/E29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F31" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="13" t="e">
+      <c r="G31" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F31" s="13">
+      <c r="H31" s="13">
         <f t="shared" si="8"/>
         <v>20.108695652173914</v>
       </c>
-      <c r="G31" s="13" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H31" s="13" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="I31" s="13" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -2208,12 +2131,8 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="13" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>12</v>
       </c>
@@ -2230,30 +2149,28 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-    </row>
-    <row r="33" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B33" s="33"/>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33"/>
-      <c r="F33" s="33" t="s">
-        <v>78</v>
-      </c>
+      <c r="F33" s="33"/>
       <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
+      <c r="H33" s="33" t="s">
+        <v>76</v>
+      </c>
       <c r="I33" s="33"/>
       <c r="J33" s="33"/>
       <c r="K33" s="33"/>
       <c r="L33" s="33"/>
       <c r="M33" s="33"/>
       <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-    </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>8</v>
       </c>
@@ -2261,51 +2178,50 @@
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
       <c r="E34" s="37"/>
-      <c r="F34" s="37">
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37">
         <v>8374</v>
       </c>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
       <c r="I34" s="37"/>
       <c r="J34" s="37"/>
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
       <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-    </row>
-    <row r="35" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" s="13" t="e">
         <f>B34/B33</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C35" s="13" t="e">
-        <f t="shared" ref="C35:O35" si="9">C34/C33</f>
+        <f t="shared" ref="C35:N35" si="9">C34/C33</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="13" t="e">
+        <f>D34/D33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E35" s="13" t="e">
+        <f>E34/E33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F35" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E35" s="13" t="e">
+      <c r="G35" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F35" s="13">
+      <c r="H35" s="13">
         <f t="shared" si="9"/>
         <v>854.48979591836724</v>
       </c>
-      <c r="G35" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H35" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="I35" s="13" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
@@ -2330,33 +2246,28 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O35" s="13" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
-      <c r="F36" s="34">
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34">
         <v>11</v>
       </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
       <c r="I36" s="34"/>
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
       <c r="L36" s="34"/>
       <c r="M36" s="34"/>
       <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-    </row>
-    <row r="37" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>8</v>
       </c>
@@ -2364,51 +2275,50 @@
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
       <c r="E37" s="37"/>
-      <c r="F37" s="37">
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37">
         <v>7539</v>
       </c>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
       <c r="I37" s="37"/>
       <c r="J37" s="37"/>
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
       <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-    </row>
-    <row r="38" spans="1:15" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:14" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="25" t="e">
         <f>B37/B36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C38" s="25" t="e">
-        <f t="shared" ref="C38:O38" si="10">C37/C36</f>
+        <f t="shared" ref="C38:N38" si="10">C37/C36</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D38" s="25" t="e">
+        <f>D37/D36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E38" s="25" t="e">
+        <f>E37/E36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F38" s="25" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E38" s="25" t="e">
+      <c r="G38" s="25" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="25">
+      <c r="H38" s="25">
         <f t="shared" si="10"/>
         <v>685.36363636363637</v>
       </c>
-      <c r="G38" s="25" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H38" s="25" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="I38" s="25" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
@@ -2433,34 +2343,30 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O38" s="25" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39" s="27">
         <f>B37+B34+B30+B27</f>
         <v>0</v>
       </c>
       <c r="C39" s="27">
-        <f t="shared" ref="C39:O39" si="11">C37+C34+C30+C27</f>
+        <f t="shared" ref="C39:N39" si="11">C37+C34+C30+C27</f>
         <v>0</v>
       </c>
       <c r="D39" s="27">
+        <f>D37+D34+D30+D27</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="27">
+        <f>E37+E34+E30+E27</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
-      </c>
-      <c r="E39" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="27">
-        <f t="shared" si="11"/>
-        <v>21405</v>
       </c>
       <c r="G39" s="27">
         <f t="shared" si="11"/>
@@ -2468,7 +2374,7 @@
       </c>
       <c r="H39" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>21405</v>
       </c>
       <c r="I39" s="27">
         <f t="shared" si="11"/>
@@ -2491,10 +2397,6 @@
         <v>0</v>
       </c>
       <c r="N39" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O39" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
